--- a/Punit/git/git-cc.xlsx
+++ b/Punit/git/git-cc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NEHA\OneDrive\Desktop\github\Html-Css-Dir\Punit\git\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Punit\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43F0BC8-05BB-41FC-9805-B04D340BFBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01824DCC-B6D8-495F-AB71-535E78E60920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3B3EADF9-5B9E-4BAE-AA0B-78923F718F1B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>GITHUB CHEAT-CODE</t>
   </si>
@@ -148,13 +148,113 @@
   </si>
   <si>
     <t>git blame &lt;file&gt;</t>
+  </si>
+  <si>
+    <t>Push Your Changes</t>
+  </si>
+  <si>
+    <r>
+      <t>Push the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier"/>
+        <family val="3"/>
+      </rPr>
+      <t>main</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.1"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> branch to the remote </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier"/>
+        <family val="3"/>
+      </rPr>
+      <t>origin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.1"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>git push origin main</t>
+  </si>
+  <si>
+    <t>Force push:</t>
+  </si>
+  <si>
+    <t>git push --force-with-lease</t>
+  </si>
+  <si>
+    <t>Push a branch that you've never pushed before:</t>
+  </si>
+  <si>
+    <t>git push -u origin &lt;name&gt;</t>
+  </si>
+  <si>
+    <t>Pull Changes</t>
+  </si>
+  <si>
+    <t>Fetch changes and then merge them into your current branch:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>git pull origin main</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB3B1B1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> OR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>git pull</t>
+    </r>
+  </si>
+  <si>
+    <t>Fetch changes (but don't change any of your local branches):</t>
+  </si>
+  <si>
+    <t>git fetch origin main</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,8 +332,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12.1"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <color theme="1"/>
+      <name val="Courier"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFB3B1B1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Courier"/>
       <family val="3"/>
     </font>
@@ -309,9 +434,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -339,14 +463,49 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD7D7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{56205C7F-2F1E-43E8-AECC-F16434129F05}">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -363,15 +522,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>78442</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>139853</xdr:rowOff>
+      <xdr:colOff>100854</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>27794</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>392208</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>117523</xdr:rowOff>
+      <xdr:colOff>414620</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>184759</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -394,7 +553,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9973236" y="1596618"/>
+          <a:off x="9995648" y="1966412"/>
           <a:ext cx="4314266" cy="1613729"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -704,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{993851C6-C2BD-42CE-8999-F70BC27D3336}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.140625" customWidth="1"/>
@@ -713,27 +872,30 @@
     <col min="4" max="4" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="3" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -741,7 +903,7 @@
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C8" t="s">
@@ -749,10 +911,10 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" t="s">
@@ -760,7 +922,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -768,126 +930,179 @@
       <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="12" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="2"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="1"/>
     </row>
     <row r="22" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="16" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>40</v>
       </c>
     </row>
+    <row r="48" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
